--- a/media/job_applications/job_applications.xlsx
+++ b/media/job_applications/job_applications.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
   <cols>
     <col width="22.84375" customWidth="1" min="1" max="1"/>
@@ -534,6 +534,43 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>swetha</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>swethaharish2222@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9047516035</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fullstack intern</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>i am seeking a strong fullstack development role</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>resumes/Resume.pdf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>07-06-2026 20:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
